--- a/out/Attention-S4_repeat_2_000008.xlsx
+++ b/out/Attention-S4_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.204705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.204705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.804705233669806</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.002580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.002580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.804705233669806</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC45" t="n">
-        <v>-6.344597622565926e-05</v>
+        <v>-7.044104561745189e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07288724076033035</v>
+        <v>-0.08092323196453005</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.08099367301014752</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.07300591571675276</v>
+        <v>-0.08112424279050377</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.1985908349058347</v>
+        <v>0.4694989373733142</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3245570557700831</v>
+        <v>0.858775601587229</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01414951870545332</v>
+        <v>0.03345170071376647</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1539467701130987</v>
+        <v>0.4554264968310988</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02481343476959829</v>
+        <v>0.05866288535123542</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1894195826663408</v>
+        <v>0.5392895869529468</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03014539280167085</v>
+        <v>0.07126878945650382</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.002580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2248949399735224</v>
+        <v>0.6231584420462654</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.007975825177535676</v>
+        <v>0.01885934233071539</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.002580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2106636515424419</v>
+        <v>0.5895176762584666</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004429021890213544</v>
+        <v>0.01047764996434483</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2115395352552771</v>
+        <v>0.5915952089679514</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.009309759768238222</v>
+        <v>0.02201340161095179</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2257348600174107</v>
+        <v>0.6251595435226639</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003653653419054096</v>
+        <v>0.008645698898478455</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2237263058163829</v>
+        <v>0.6204176933530536</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00260137698924692</v>
+        <v>0.006156468302839179</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2252726703538843</v>
+        <v>0.624080115012852</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001020207855128424</v>
+        <v>0.002420193681138232</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2247110393784933</v>
+        <v>0.622759238729429</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0005776541771295794</v>
+        <v>0.001371481958139456</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2248441837985325</v>
+        <v>0.6230805957852356</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002169557845988454</v>
+        <v>0.000518768676884048</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2246999754054952</v>
+        <v>0.6227467259548433</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>9.849028168112019e-05</v>
+        <v>0.0002405141788818064</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2246809440103266</v>
+        <v>0.6227085395717398</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.294428883463679e-05</v>
+        <v>8.542043296764513e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2246479615048307</v>
+        <v>0.6226375584235089</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>2.171120209290413e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2246270682849542</v>
+        <v>0.6225954742437971</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.238290199080266e-07</v>
+        <v>8.355601046452064e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2246220593492498</v>
+        <v>0.62259045339382</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>2.191662034084867e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2246174955987104</v>
+        <v>0.6225864713092278</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-1.195152058104458e-07</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2246135950257715</v>
+        <v>0.6225840366390371</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-4.376196673809899e-06</v>
+        <v>-3.128590021429696e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.602580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2246083736137857</v>
+        <v>0.6225785193970473</v>
       </c>
     </row>
     <row r="79">
@@ -63738,7 +63738,7 @@
         <v>0</v>
       </c>
       <c r="IY79" t="n">
-        <v>-4.70653621650487e-06</v>
+        <v>-4.413072433009741e-06</v>
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.224602711616782</v>
+        <v>0.6225721954030394</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2246025278743228</v>
+        <v>0.622566827614461</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2246025646228145</v>
+        <v>0.6225668643629527</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2246026748682901</v>
+        <v>0.6225669746084284</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.804705233669806</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2246027483652737</v>
+        <v>0.622567048105412</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.002580650042519</v>
+        <v>1.668078547550069</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2246029321077329</v>
+        <v>0.6225672318478711</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2246044755443893</v>
+        <v>0.6225687752845276</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2246059454840624</v>
+        <v>0.6225702452242007</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2246071949327844</v>
+        <v>0.6225714946729226</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2246085546269817</v>
+        <v>0.62257285436712</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2246063497174725</v>
+        <v>0.6225706494576106</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2246059454840624</v>
+        <v>0.6225702452242007</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2246051002687504</v>
+        <v>0.6225694000088887</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2246056514961277</v>
+        <v>0.6225699512362659</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2246053207597013</v>
+        <v>0.6225696204998395</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2246050267717668</v>
+        <v>0.6225693265119051</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2246051002687504</v>
+        <v>0.6225694000088887</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2246046592868485</v>
+        <v>0.6225689590269867</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2246045490413729</v>
+        <v>0.6225688487815112</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2246045122928813</v>
+        <v>0.6225688120330195</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2246046592868485</v>
+        <v>0.6225689590269867</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2246041815564549</v>
+        <v>0.6225684812965931</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2246051370172421</v>
+        <v>0.6225694367573804</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.204705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2246051002687504</v>
+        <v>0.6225694000088887</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2246047695323241</v>
+        <v>0.6225690692724622</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.224605210514226</v>
+        <v>0.6225695102543642</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2246045857898649</v>
+        <v>0.6225688855300031</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2246044020474057</v>
+        <v>0.622568701787544</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2246039978139957</v>
+        <v>0.6225682975541339</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2246031525986837</v>
+        <v>0.6225674523388219</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.224603115850192</v>
+        <v>0.6225674155903302</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2246032628441593</v>
+        <v>0.6225675625842975</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2246031893471757</v>
+        <v>0.6225674890873139</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.602580650042519</v>
+        <v>2.268078547550068</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2246032628441593</v>
+        <v>0.6225675625842975</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2246032995926512</v>
+        <v>0.6225675993327894</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.6958951686397941</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2246031893471757</v>
+        <v>0.6225674890873139</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2246036303290776</v>
+        <v>0.6225679300692158</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.224603520083602</v>
+        <v>0.6225678198237403</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2246034833351101</v>
+        <v>0.6225677830752484</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2246034098381265</v>
+        <v>0.6225677095782647</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2246033730896348</v>
+        <v>0.622567672829773</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2246031525986837</v>
+        <v>0.6225674523388219</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2246030791017001</v>
+        <v>0.6225673788418383</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2246030056047165</v>
+        <v>0.6225673053448547</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2246030423532084</v>
+        <v>0.6225673420933466</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2246029321077329</v>
+        <v>0.6225672318478711</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.602580650042519</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2246030423532084</v>
+        <v>0.6225673420933466</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.804705233669806</v>
+        <v>-1.295895168639794</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2246033363411429</v>
+        <v>0.6225676360812811</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000008.xlsx
+++ b/out/Attention-S4_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.002580650042519</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.204705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.204705233669806</v>
+        <v>0.9917978745164386</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC45" t="n">
-        <v>-6.344597622565926e-05</v>
+        <v>-9.335025654442143e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.07288724076033035</v>
+        <v>-0.1072415152000247</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.072950686736556</v>
+        <v>-0.1073348654565691</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.07300591571675276</v>
+        <v>-0.1074031187910816</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.1985908349058347</v>
+        <v>0.2454234468510486</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3245570557700831</v>
+        <v>0.3839149969160682</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01414951870545332</v>
+        <v>0.0174863324737656</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1539467701130987</v>
+        <v>0.1730706022005174</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02481343476959829</v>
+        <v>0.03066506919631582</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.1894195826663408</v>
+        <v>0.216908756266643</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03014539280167085</v>
+        <v>0.03725474934412477</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.2248949399735224</v>
+        <v>0.260750011297181</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.007975825177535676</v>
+        <v>0.009857783787164724</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.7331981600291557</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2106636515424419</v>
+        <v>0.2431640213909575</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004429021890213544</v>
+        <v>0.005474608716881474</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2115395352552771</v>
+        <v>0.2442476263168969</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.009309759768238222</v>
+        <v>0.01150627353122672</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2257348600174107</v>
+        <v>0.261791530060669</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.003653653419054096</v>
+        <v>0.004517148913190333</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2237263058163829</v>
+        <v>0.2593105166820453</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00260137698924692</v>
+        <v>0.00321545389736863</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2252726703538843</v>
+        <v>0.2612223913289781</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001020207855128424</v>
+        <v>0.00126191248852294</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2247110393784933</v>
+        <v>0.2605296147889458</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0005776541771295794</v>
+        <v>0.0007148399489934221</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2248441837985325</v>
+        <v>0.2606952852761368</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002169557845988454</v>
+        <v>0.0002686280307488412</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2246999754054952</v>
+        <v>0.2605183010950405</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>9.849028168112019e-05</v>
+        <v>0.0001238123718796922</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2246809440103266</v>
+        <v>0.2604959279664483</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.294428883463679e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2246479615048307</v>
+        <v>0.2604564651696086</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.447658039816054e-06</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2246270682849542</v>
+        <v>0.2604319301258314</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>7.238290199080266e-07</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2246220593492498</v>
+        <v>0.2604269189562006</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2246174955987104</v>
+        <v>0.2604224646623963</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2246135950257715</v>
+        <v>0.2604189305651444</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-4.376196673809899e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2246083736137857</v>
+        <v>0.2604136347351402</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.224602711616782</v>
+        <v>0.2604079727381365</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2246025278743228</v>
+        <v>0.2604077889956773</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2246025646228145</v>
+        <v>0.260407825744169</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2246026748682901</v>
+        <v>0.2604079359896446</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2246027483652737</v>
+        <v>0.2604080094866282</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.002580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2246029321077329</v>
+        <v>0.2604081932290874</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2246044755443893</v>
+        <v>0.2604097366657439</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2246059454840624</v>
+        <v>0.2604112066054169</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2246071949327844</v>
+        <v>0.2604124560541389</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2246085546269817</v>
+        <v>0.2604138157483363</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.602580650042519</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2246063497174725</v>
+        <v>0.260411610838827</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2246059454840624</v>
+        <v>0.2604112066054169</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2246051002687504</v>
+        <v>0.260410361390105</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2246056514961277</v>
+        <v>0.2604109126174822</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2246053207597013</v>
+        <v>0.2604105818810558</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2246050267717668</v>
+        <v>0.2604102878931214</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2246051002687504</v>
+        <v>0.260410361390105</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2246046592868485</v>
+        <v>0.260409920408203</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2246045490413729</v>
+        <v>0.2604098101627275</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2246045122928813</v>
+        <v>0.2604097734142358</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2246046592868485</v>
+        <v>0.260409920408203</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2246041815564549</v>
+        <v>0.2604094426778094</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2246051370172421</v>
+        <v>0.2604103981385967</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>1.204705233669806</v>
+        <v>0.3501325296679072</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2246051002687504</v>
+        <v>0.260410361390105</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2246047695323241</v>
+        <v>0.2604100306536786</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.224605210514226</v>
+        <v>0.2604104716355805</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2246045857898649</v>
+        <v>0.2604098469112194</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2246044020474057</v>
+        <v>0.2604096631687602</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.804705233669806</v>
+        <v>1.191797874516439</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2246039978139957</v>
+        <v>0.2604092589353502</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>1.804705233669806</v>
+        <v>0.5501325296679072</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2246031525986837</v>
+        <v>0.2604084137200383</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.224603115850192</v>
+        <v>0.2604083769715466</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2246032628441593</v>
+        <v>0.2604085239655138</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2246031893471757</v>
+        <v>0.2604084504685302</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2246032628441593</v>
+        <v>0.2604085239655138</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>1.204705233669806</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2246032995926512</v>
+        <v>0.2604085607140057</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.2915328151806243</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2246031893471757</v>
+        <v>0.2604084504685302</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2246036303290776</v>
+        <v>0.2604088914504321</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.224603520083602</v>
+        <v>0.2604087812049566</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2246034833351101</v>
+        <v>0.2604087444564647</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2246034098381265</v>
+        <v>0.2604086709594811</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2246033730896348</v>
+        <v>0.2604086342109894</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2246031525986837</v>
+        <v>0.2604084137200383</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2246030791017001</v>
+        <v>0.2604083402230546</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2246030056047165</v>
+        <v>0.260408266726071</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2246030423532084</v>
+        <v>0.260408303474563</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.9331981600291558</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2246029321077329</v>
+        <v>0.2604081932290874</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.602580650042519</v>
+        <v>-0.09153281518062434</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2246030423532084</v>
+        <v>0.260408303474563</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>1.804705233669806</v>
+        <v>0.2292998572436414</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2246033363411429</v>
+        <v>0.2604085974624974</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-S4_repeat_2_000008.xlsx
+++ b/out/Attention-S4_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>1</v>
+        <v>0.01476840302348137</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.3</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.01069439575076103</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.37</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.01039678975939751</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001342426985502243</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.003901023417711258</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.002336319535970688</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.001394219696521759</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.09153281518062434</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0007547289133071899</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0009799115359783173</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.0006569698452949524</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0005408935248851776</v>
       </c>
       <c r="JB12" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.3</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.002724945545196533</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.002443484961986542</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.0007741451263427734</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.001134075224399567</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.003648009151220322</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.001623295247554779</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.191797874516439</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001728471368551254</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.191797874516439</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.002791576087474823</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.191797874516439</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002148054540157318</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.0001927874982357025</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.002162132412195206</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.0008610114455223083</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>2.868101000785828e-05</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.002875491976737976</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.191797874516439</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.003364801406860352</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.005174312740564346</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.004714269191026688</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.003290969878435135</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.005800094455480576</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.002066429704427719</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.01163303479552269</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.008843060582876205</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.005571793764829636</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.009361471980810165</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.01071199402213097</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.01281480118632317</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.009629096835851669</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.006893660873174667</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.9917978745164386</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.007227834314107895</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.16</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.007937435060739517</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.9917978745164386</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.003269415348768234</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.002049997448921204</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.005860481411218643</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-9.335025654442143e-05</v>
+        <v>-8.038386143534444e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1072415152000247</v>
+        <v>-0.09234561764556547</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.004270549863576889</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.00413026288151741</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.0009541697800159454</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0001181885600090027</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.00137503445148468</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.0031932033598423</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.003708548843860626</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.004411142319440842</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.005739957094192505</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.005817513912916183</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.006518896669149399</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.003739424049854279</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.004779975861310959</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1073348654565691</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.005714345723390579</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1074031187910816</v>
+        <v>-0.09249386541326216</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2454234468510486</v>
+        <v>0.2440231515484895</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.002492580562829971</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.09153281518062434</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3839149969160682</v>
+        <v>0.3960209710705117</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0174863324737656</v>
+        <v>0.01738659831372416</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.0002287589013576508</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1730706022005174</v>
+        <v>0.1863795762300433</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03066506919631582</v>
+        <v>0.03049004114144887</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.000849597156047821</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.216908756266643</v>
+        <v>0.2299675148270323</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03725474934412477</v>
+        <v>0.03704211092811067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.002184949815273285</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.09153281518062434</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.260750011297181</v>
+        <v>0.2735585377344215</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.009857783787164724</v>
+        <v>0.009801325028875854</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.00180952250957489</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.7331981600291557</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2431640213909575</v>
+        <v>0.2560728948845177</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005474608716881474</v>
+        <v>0.005443424548366816</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.004644021391868591</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2442476263168969</v>
+        <v>0.2571503046163819</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01150627353122672</v>
+        <v>0.01143999276504531</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.009066469967365265</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.261791530060669</v>
+        <v>0.2745943394724466</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004517148913190333</v>
+        <v>0.004491716367079728</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.009285800158977509</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2593105166820453</v>
+        <v>0.2721272511824546</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.00321545389736863</v>
+        <v>0.003196479610881724</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.00631694495677948</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2612223913289781</v>
+        <v>0.2740283464565771</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00126191248852294</v>
+        <v>0.001255123032528712</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.007203225046396255</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.2605296147889458</v>
+        <v>0.27333925378072</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007148399489934221</v>
+        <v>0.0007102157094923938</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.005979523062705994</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2606952852761368</v>
+        <v>0.2735040116260843</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002686280307488412</v>
+        <v>0.0002674536615181594</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003270626068115234</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.3</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2605183010950405</v>
+        <v>0.2733277639973322</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001238123718796922</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.002583973109722137</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2604959279664483</v>
+        <v>0.2733054658600348</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.001303944736719131</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2604564651696086</v>
+        <v>0.2732660030631952</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.002048853784799576</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2604319301258314</v>
+        <v>0.273241468019418</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003677185624837875</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2604269189562006</v>
+        <v>0.2732364568497871</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.01013768091797829</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.2604224646623963</v>
+        <v>0.2732320025559829</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00995337963104248</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2604189305651444</v>
+        <v>0.2732284684587309</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.007459066808223724</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.09153281518062434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2604136347351402</v>
+        <v>0.2732231726287268</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.0001698993146419525</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2604079727381365</v>
+        <v>0.2732175106317231</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.0005597919225692749</v>
       </c>
       <c r="JB80" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2604077889956773</v>
+        <v>0.2732173268892639</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.01252875849604607</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.260407825744169</v>
+        <v>0.2732173636377556</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.006058182567358017</v>
       </c>
       <c r="JB82" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2604079359896446</v>
+        <v>0.2732174738832311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.004388298839330673</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2604080094866282</v>
+        <v>0.2732175473802148</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.002984035760164261</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.09153281518062434</v>
+        <v>0.3</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2604081932290874</v>
+        <v>0.2732177311226739</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.01067093759775162</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2604097366657439</v>
+        <v>0.2732192745593304</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.01642151921987534</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2604112066054169</v>
+        <v>0.2732207444990035</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.002316765487194061</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2604124560541389</v>
+        <v>0.2732219939477255</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.01676950976252556</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2604138157483363</v>
+        <v>0.2732233536419228</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.01245586201548576</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.3501325296679072</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.260411610838827</v>
+        <v>0.2732211487324135</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.009177815169095993</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2604112066054169</v>
+        <v>0.2732207444990035</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.02374095842242241</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.260410361390105</v>
+        <v>0.2732198992836916</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.02620428428053856</v>
       </c>
       <c r="JB92" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2604109126174822</v>
+        <v>0.2732204505110688</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.01582690700888634</v>
       </c>
       <c r="JB93" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2604105818810558</v>
+        <v>0.2732201197746424</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.01324538514018059</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.191797874516439</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.2604102878931214</v>
+        <v>0.2732198257867079</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.001744356006383896</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.5501325296679072</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.260410361390105</v>
+        <v>0.2732198992836916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.005895726382732391</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.260409920408203</v>
+        <v>0.2732194583017896</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.001660268753767014</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2604098101627275</v>
+        <v>0.273219348056314</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.01541638746857643</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2604097734142358</v>
+        <v>0.2732193113078223</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.01227820664644241</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.260409920408203</v>
+        <v>0.2732194583017896</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.008692391216754913</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2604094426778094</v>
+        <v>0.2732189805713959</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.006431166082620621</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2604103981385967</v>
+        <v>0.2732199360321833</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.00253237783908844</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.3501325296679072</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.260410361390105</v>
+        <v>0.2732198992836916</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.01149897649884224</v>
       </c>
       <c r="JB103" t="n">
-        <v>1.191797874516439</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2604100306536786</v>
+        <v>0.2732195685472651</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.01540736481547356</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2604104716355805</v>
+        <v>0.2732200095291671</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.0183154009282589</v>
       </c>
       <c r="JB105" t="n">
-        <v>1.191797874516439</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2604098469112194</v>
+        <v>0.273219384804806</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.01494896039366722</v>
       </c>
       <c r="JB106" t="n">
-        <v>1.191797874516439</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.2604096631687602</v>
+        <v>0.2732192010623468</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.01484480127692223</v>
       </c>
       <c r="JB107" t="n">
-        <v>1.191797874516439</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2604092589353502</v>
+        <v>0.2732187968289368</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.009479377418756485</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.5501325296679072</v>
+        <v>0.3</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2604084137200383</v>
+        <v>0.2732179516136248</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01025982573628426</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2604083769715466</v>
+        <v>0.2732179148651331</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.0125744640827179</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2604085239655138</v>
+        <v>0.2732180618591004</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.01119063422083855</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2604084504685302</v>
+        <v>0.2732179883621167</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003424912691116333</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2604085239655138</v>
+        <v>0.2732180618591004</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.0007463730871677399</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2604085607140057</v>
+        <v>0.2732180986075923</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.001957148313522339</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.2915328151806243</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2604084504685302</v>
+        <v>0.2732179883621167</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003918521106243134</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2604088914504321</v>
+        <v>0.2732184293440187</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003837957978248596</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2604087812049566</v>
+        <v>0.2732183190985432</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.005759056657552719</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2604087444564647</v>
+        <v>0.2732182823500512</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.005949176847934723</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2604086709594811</v>
+        <v>0.2732182088530676</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.0143539272248745</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.2604086342109894</v>
+        <v>0.2732181721045759</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.02228942885994911</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2604084137200383</v>
+        <v>0.2732179516136248</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.02144064754247665</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2604083402230546</v>
+        <v>0.2732178781166412</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.01949825137853622</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.260408266726071</v>
+        <v>0.2732178046196576</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.01051713153719902</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.9331981600291558</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.260408303474563</v>
+        <v>0.2732178413681495</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.006765503436326981</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.9331981600291558</v>
+        <v>0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2604081932290874</v>
+        <v>0.2732177311226739</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.003204971551895142</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.09153281518062434</v>
+        <v>0.5800000000000005</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.260408303474563</v>
+        <v>0.2732178413681495</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.001132681965827942</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2292998572436414</v>
+        <v>1.000000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2604085974624974</v>
+        <v>0.273218135356084</v>
       </c>
     </row>
   </sheetData>
